--- a/Stats Sheet/Round Gaps/At War.xlsx
+++ b/Stats Sheet/Round Gaps/At War.xlsx
@@ -85,7 +85,7 @@
     <x:t>250</x:t>
   </x:si>
   <x:si>
-    <x:t>LqndSlide</x:t>
+    <x:t>lqndslide</x:t>
   </x:si>
   <x:si>
     <x:t>patriotsfan75</x:t>
